--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89D301EB-47CD-4A71-9BE5-43D9550FF799}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BFAEBC2-88AB-45D6-BD41-1032440A8886}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>I have speaked current affair in front of class.</t>
   </si>
 </sst>
 </file>
@@ -1032,27 +1038,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>90</v>
+      </c>
+      <c r="E7" s="14">
+        <v>180</v>
+      </c>
+      <c r="F7" s="14">
+        <v>250</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>60</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BFAEBC2-88AB-45D6-BD41-1032440A8886}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85170B5D-8F11-4B80-93CC-51C0DA745442}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>I have speaked current affair in front of class.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>celebrated independence day.</t>
   </si>
 </sst>
 </file>
@@ -1085,26 +1094,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="14">
+        <v>510</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>210</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>180</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85170B5D-8F11-4B80-93CC-51C0DA745442}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5CF68E-9640-4A79-96B8-4E200BB24583}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>celebrated independence day.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>stayed whole Day at home</t>
   </si>
 </sst>
 </file>
@@ -1140,26 +1146,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="14">
+        <v>540</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>180</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>200</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5CF68E-9640-4A79-96B8-4E200BB24583}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2631E8AF-BCF9-42FE-B4DB-570D650DCFF5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>stayed whole Day at home</t>
+  </si>
+  <si>
+    <t>learned many new things.</t>
   </si>
 </sst>
 </file>
@@ -1192,26 +1195,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>25</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>150</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>100</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2631E8AF-BCF9-42FE-B4DB-570D650DCFF5}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70587DF1-3E90-40B1-A0CE-5FA2B8853306}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>learned many new things.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>attended 9:30 to 5:00pm all day classes</t>
   </si>
 </sst>
 </file>
@@ -1240,27 +1246,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>150</v>
+      </c>
+      <c r="E11" s="14">
+        <v>150</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70587DF1-3E90-40B1-A0CE-5FA2B8853306}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE8D5E7-1D1A-4602-9CF7-E80F1D03F5BA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>attended 9:30 to 5:00pm all day classes</t>
+  </si>
+  <si>
+    <t>done group discussion in communication class.</t>
   </si>
 </sst>
 </file>
@@ -1292,27 +1295,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>210</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE8D5E7-1D1A-4602-9CF7-E80F1D03F5BA}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B61699-0304-41F0-B7E3-0C1B2AC6262E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1342,25 +1342,47 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>200</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B61699-0304-41F0-B7E3-0C1B2AC6262E}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8CD7ED-A75A-4872-B088-21B3ECE0D4AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>done group discussion in communication class.</t>
+  </si>
+  <si>
+    <t>learned new tricks for analytical problem solving.</t>
+  </si>
+  <si>
+    <t>felt satisfied.</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1347,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46254</v>
       </c>
@@ -1383,29 +1389,55 @@
       <c r="M13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>200</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8CD7ED-A75A-4872-B088-21B3ECE0D4AA}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7775D1-51BA-41A8-AE3F-543F25163962}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>felt satisfied.</t>
+  </si>
+  <si>
+    <t>learned Python basics.</t>
   </si>
 </sst>
 </file>
@@ -1440,26 +1443,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B15" s="14">
+        <v>510</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>250</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7775D1-51BA-41A8-AE3F-543F25163962}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750D3AFB-7E56-4D04-ACC5-A13FB5A434A2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>learned Python basics.</t>
+  </si>
+  <si>
+    <t>Learned SQLbasics</t>
   </si>
 </sst>
 </file>
@@ -1489,26 +1492,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B16" s="14">
+        <v>520</v>
+      </c>
+      <c r="C16" s="14">
+        <v>50</v>
+      </c>
+      <c r="D16" s="14">
+        <v>150</v>
+      </c>
+      <c r="E16" s="14">
+        <v>220</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>150</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{750D3AFB-7E56-4D04-ACC5-A13FB5A434A2}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{848F662E-5A1B-46E3-8A20-C0F3255CA1F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Learned SQLbasics</t>
+  </si>
+  <si>
+    <t>done mini python tasks.</t>
   </si>
 </sst>
 </file>
@@ -1538,26 +1541,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B17" s="14">
+        <v>400</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>220</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{848F662E-5A1B-46E3-8A20-C0F3255CA1F9}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C83C2E-74A6-41DB-B0CD-008D7F1BE2B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>done mini python tasks.</t>
+  </si>
+  <si>
+    <t>done some MERN project work.</t>
   </si>
 </sst>
 </file>
@@ -1587,26 +1590,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>250</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>150</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C83C2E-74A6-41DB-B0CD-008D7F1BE2B8}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F341F3C0-A8A2-43B3-8125-848703547B36}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>done some MERN project work.</t>
+  </si>
+  <si>
+    <t>not able to utilize day.</t>
   </si>
 </sst>
 </file>
@@ -1636,26 +1639,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>210</v>
+      </c>
+      <c r="E19" s="14">
+        <v>180</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>100</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F341F3C0-A8A2-43B3-8125-848703547B36}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E24210A-4301-4673-A7EC-44906D5EFD93}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>not able to utilize day.</t>
+  </si>
+  <si>
+    <t>improved UI of my MERN project.</t>
   </si>
 </sst>
 </file>
@@ -1684,27 +1687,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>210</v>
+      </c>
+      <c r="E20" s="14">
+        <v>210</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E24210A-4301-4673-A7EC-44906D5EFD93}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009753FC-B002-42F0-8524-CADC44BF3FE1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>improved UI of my MERN project.</t>
+  </si>
+  <si>
+    <t>celebrated Rakhi</t>
   </si>
 </sst>
 </file>
@@ -1734,26 +1737,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>210</v>
+      </c>
+      <c r="E21" s="14">
+        <v>180</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>100</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009753FC-B002-42F0-8524-CADC44BF3FE1}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32F5C2FF-2376-43F8-8011-57DC9ADF07AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>celebrated Rakhi</t>
+  </si>
+  <si>
+    <t>Utilized Saturday with some coding.</t>
   </si>
 </sst>
 </file>
@@ -1782,27 +1785,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B22" s="14">
+        <v>510</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>210</v>
+      </c>
+      <c r="E22" s="14">
+        <v>250</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32F5C2FF-2376-43F8-8011-57DC9ADF07AC}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2BFADA8-A566-4A9A-BD84-3998BEFA3F6C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Utilized Saturday with some coding.</t>
+  </si>
+  <si>
+    <t>done some revision.</t>
   </si>
 </sst>
 </file>
@@ -1832,26 +1835,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B23" s="14">
+        <v>540</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>210</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2BFADA8-A566-4A9A-BD84-3998BEFA3F6C}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9417F74B-A641-46B4-A241-90AD787CE644}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>done some revision.</t>
+  </si>
+  <si>
+    <t>done individual presentation practice.</t>
   </si>
 </sst>
 </file>
@@ -1880,27 +1883,51 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>180</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9417F74B-A641-46B4-A241-90AD787CE644}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA71B6B1-8203-43B9-8745-6EA327B4B8C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>done individual presentation practice.</t>
+  </si>
+  <si>
+    <t>Learned about AI and ML.</t>
   </si>
 </sst>
 </file>
@@ -1930,26 +1933,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>230</v>
+      </c>
+      <c r="E25" s="14">
+        <v>210</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA71B6B1-8203-43B9-8745-6EA327B4B8C2}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{923E0C3C-D347-4FD4-9645-C40C5B61202C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Learned about AI and ML.</t>
+  </si>
+  <si>
+    <t>felt tired all day.</t>
   </si>
 </sst>
 </file>
@@ -1979,26 +1982,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>210</v>
+      </c>
+      <c r="E26" s="14">
+        <v>240</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{923E0C3C-D347-4FD4-9645-C40C5B61202C}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A589FE0-3B52-43EF-A9E3-15C98F4C2BA9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>felt tired all day.</t>
+  </si>
+  <si>
+    <t>Got late and missed communication class.</t>
   </si>
 </sst>
 </file>
@@ -2027,27 +2030,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>250</v>
+      </c>
+      <c r="E27" s="14">
+        <v>210</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A589FE0-3B52-43EF-A9E3-15C98F4C2BA9}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5043146D-40FA-482B-B8D1-9EF1D5277A14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Got late and missed communication class.</t>
+  </si>
+  <si>
+    <t>Celebrated janamashtmi with family.</t>
   </si>
 </sst>
 </file>
@@ -2032,7 +2035,7 @@
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>2026</v>
+        <v>46268</v>
       </c>
       <c r="B27" s="14">
         <v>420</v>
@@ -2076,27 +2079,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="14">
+        <v>400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>250</v>
+      </c>
+      <c r="E28" s="14">
+        <v>180</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5043146D-40FA-482B-B8D1-9EF1D5277A14}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556D6DA8-7466-40F3-A9EE-AF25E9E5D030}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Celebrated janamashtmi with family.</t>
+  </si>
+  <si>
+    <t>Utilized Saturday by learning new things.</t>
   </si>
 </sst>
 </file>
@@ -2125,27 +2128,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="14">
+        <v>510</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>210</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>310</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556D6DA8-7466-40F3-A9EE-AF25E9E5D030}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67CB2D-5D45-4B76-8D1C-54F9C4158FCE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Utilized Saturday by learning new things.</t>
+  </si>
+  <si>
+    <t>learned pandas.</t>
   </si>
 </sst>
 </file>
@@ -2175,26 +2178,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="14">
+        <v>530</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>210</v>
+      </c>
+      <c r="E30" s="14">
+        <v>250</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>250</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67CB2D-5D45-4B76-8D1C-54F9C4158FCE}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0535F471-F0C8-4706-8718-D38EB3C63111}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>learned pandas.</t>
+  </si>
+  <si>
+    <t>learned percentage and profit and loss.</t>
   </si>
 </sst>
 </file>
@@ -2223,27 +2226,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>230</v>
+      </c>
+      <c r="E31" s="14">
+        <v>220</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>200</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0535F471-F0C8-4706-8718-D38EB3C63111}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55FCC16E-F5F3-43D8-9064-F15D2B7DC1D3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>learned percentage and profit and loss.</t>
+  </si>
+  <si>
+    <t>prepared for DBMS CA.</t>
   </si>
 </sst>
 </file>
@@ -2273,26 +2276,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>250</v>
+      </c>
+      <c r="E32" s="14">
+        <v>240</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>180</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55FCC16E-F5F3-43D8-9064-F15D2B7DC1D3}"/>
+  <xr:revisionPtr revIDLastSave="360" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E40A3689-9071-4BEB-BF1B-A2E3703B094E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>prepared for DBMS CA.</t>
+  </si>
+  <si>
+    <t>Given DBMS CA.</t>
   </si>
 </sst>
 </file>
@@ -2322,26 +2325,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>220</v>
+      </c>
+      <c r="E33" s="14">
+        <v>180</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E40A3689-9071-4BEB-BF1B-A2E3703B094E}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED790ED-AFC7-4216-A1BA-91DFC135003D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Given DBMS CA.</t>
+  </si>
+  <si>
+    <t>had given communication skills CA1.</t>
   </si>
 </sst>
 </file>
@@ -2370,27 +2373,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="14">
+        <v>400</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
+        <v>180</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>200</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED790ED-AFC7-4216-A1BA-91DFC135003D}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F2CE9BD-7737-445C-90C1-C96CC036BE58}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>had given communication skills CA1.</t>
+  </si>
+  <si>
+    <t>The CA of communication does not gone well.</t>
   </si>
 </sst>
 </file>
@@ -2419,27 +2422,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>230</v>
+      </c>
+      <c r="E35" s="14">
+        <v>200</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>230</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F2CE9BD-7737-445C-90C1-C96CC036BE58}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C16A366-A180-4F59-BAB4-7A82EEB0FE09}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>The CA of communication does not gone well.</t>
+  </si>
+  <si>
+    <t>done some practice of improving communication skills.</t>
   </si>
 </sst>
 </file>
@@ -2468,27 +2471,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="14">
+        <v>510</v>
+      </c>
+      <c r="C36" s="14">
+        <v>50</v>
+      </c>
+      <c r="D36" s="14">
+        <v>250</v>
+      </c>
+      <c r="E36" s="14">
+        <v>240</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>300</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C16A366-A180-4F59-BAB4-7A82EEB0FE09}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4227563E-F130-482A-B8F0-E7DA7627FE9E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>done some practice of improving communication skills.</t>
+  </si>
+  <si>
+    <t>spent time with family.</t>
   </si>
 </sst>
 </file>
@@ -2518,26 +2521,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="14">
+        <v>550</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>200</v>
+      </c>
+      <c r="E37" s="14">
+        <v>180</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>300</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4227563E-F130-482A-B8F0-E7DA7627FE9E}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF32BD9-89FD-45D6-8143-54EC9C684395}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>spent time with family.</t>
+  </si>
+  <si>
+    <t>result annouced for DBMS CA1</t>
   </si>
 </sst>
 </file>
@@ -2567,26 +2570,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>210</v>
+      </c>
+      <c r="E38" s="14">
+        <v>240</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF32BD9-89FD-45D6-8143-54EC9C684395}"/>
+  <xr:revisionPtr revIDLastSave="432" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D952594-EFD2-402F-8B23-69163BD9A962}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>result annouced for DBMS CA1</t>
+  </si>
+  <si>
+    <t>build a mini ML project</t>
   </si>
 </sst>
 </file>
@@ -2616,26 +2619,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>210</v>
+      </c>
+      <c r="E39" s="14">
+        <v>250</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D952594-EFD2-402F-8B23-69163BD9A962}"/>
+  <xr:revisionPtr revIDLastSave="457" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D8F1F7-96D8-432E-979C-E7711989EECF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>build a mini ML project</t>
+  </si>
+  <si>
+    <t>speaked current affair in front of class.</t>
   </si>
 </sst>
 </file>
@@ -2665,48 +2668,96 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="14">
+        <v>440</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>180</v>
+      </c>
+      <c r="E40" s="14">
+        <v>180</v>
+      </c>
+      <c r="F40" s="14">
+        <v>250</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>200</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>190</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>220</v>
+      </c>
+      <c r="E41" s="14">
+        <v>180</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>300</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="457" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D8F1F7-96D8-432E-979C-E7711989EECF}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB78F415-8FA7-4341-9C87-1612C771796E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>speaked current affair in front of class.</t>
+  </si>
+  <si>
+    <t>preparing of analytical skills CA.</t>
   </si>
 </sst>
 </file>
@@ -2760,26 +2763,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="14">
+        <v>410</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>220</v>
+      </c>
+      <c r="E42" s="14">
+        <v>180</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>250</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB78F415-8FA7-4341-9C87-1612C771796E}"/>
+  <xr:revisionPtr revIDLastSave="481" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7F2AC7-1633-46D1-9D88-0340CD843F32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>preparing of analytical skills CA.</t>
+  </si>
+  <si>
+    <t>given ANALYTICAL SKILLS CA.</t>
   </si>
 </sst>
 </file>
@@ -2809,26 +2812,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="14">
+        <v>410</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>150</v>
+      </c>
+      <c r="F43" s="14">
+        <v>100</v>
+      </c>
+      <c r="G43" s="14">
+        <v>2</v>
+      </c>
+      <c r="H43" s="14">
+        <v>350</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="481" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7F2AC7-1633-46D1-9D88-0340CD843F32}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC08E983-075B-4AE6-B9DA-93277B49CC1C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>given ANALYTICAL SKILLS CA.</t>
+  </si>
+  <si>
+    <t>done some coding .</t>
   </si>
 </sst>
 </file>
@@ -2858,26 +2861,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="14">
+        <v>520</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>220</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>300</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC08E983-075B-4AE6-B9DA-93277B49CC1C}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{412F799D-2833-4E01-91C8-6DF45D1106E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Month:</t>
-  </si>
-  <si>
-    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
   </si>
   <si>
     <t>Date</t>
@@ -334,6 +331,9 @@
   </si>
   <si>
     <t>done some coding .</t>
+  </si>
+  <si>
+    <t>CA 2 annouced for DBMS.</t>
   </si>
 </sst>
 </file>
@@ -951,7 +951,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -1021,7 +1021,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1038,7 +1038,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1046,13 +1046,13 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>34</v>
+      <c r="A4" s="18">
+        <v>20</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1070,46 +1070,46 @@
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1146,16 +1146,16 @@
         <v>390</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="N6" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1192,16 +1192,16 @@
         <v>350</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1238,16 +1238,16 @@
         <v>450</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1284,16 +1284,16 @@
         <v>430</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="N9" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1330,16 +1330,16 @@
         <v>265</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N10" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1376,16 +1376,16 @@
         <v>210</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>65</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1422,16 +1422,16 @@
         <v>170</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1468,16 +1468,16 @@
         <v>290</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1514,16 +1514,16 @@
         <v>390</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N14" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1560,16 +1560,16 @@
         <v>410</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>60</v>
-      </c>
       <c r="N15" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1606,16 +1606,16 @@
         <v>350</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N16" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1652,16 +1652,16 @@
         <v>220</v>
       </c>
       <c r="K17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N17" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1698,16 +1698,16 @@
         <v>140</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1744,16 +1744,16 @@
         <v>230</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1790,16 +1790,16 @@
         <v>250</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1836,16 +1836,16 @@
         <v>220</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1882,16 +1882,16 @@
         <v>290</v>
       </c>
       <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>60</v>
-      </c>
       <c r="N22" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1928,16 +1928,16 @@
         <v>300</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1974,16 +1974,16 @@
         <v>260</v>
       </c>
       <c r="K24" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N24" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2020,16 +2020,16 @@
         <v>210</v>
       </c>
       <c r="K25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N25" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2066,16 +2066,16 @@
         <v>170</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2112,16 +2112,16 @@
         <v>240</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N27" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2158,16 +2158,16 @@
         <v>190</v>
       </c>
       <c r="K28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L28" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M28" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2204,16 +2204,16 @@
         <v>230</v>
       </c>
       <c r="K29" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L29" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N29" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2250,16 +2250,16 @@
         <v>170</v>
       </c>
       <c r="K30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L30" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M30" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2296,16 +2296,16 @@
         <v>90</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N31" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2342,16 +2342,16 @@
         <v>100</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L32" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N32" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2388,16 +2388,16 @@
         <v>190</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2434,16 +2434,16 @@
         <v>160</v>
       </c>
       <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>60</v>
-      </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2480,16 +2480,16 @@
         <v>80</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2526,16 +2526,16 @@
         <v>90</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2572,16 +2572,16 @@
         <v>150</v>
       </c>
       <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L37" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M37" s="16" t="s">
-        <v>60</v>
-      </c>
       <c r="N37" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2618,16 +2618,16 @@
         <v>110</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2664,16 +2664,16 @@
         <v>110</v>
       </c>
       <c r="K39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L39" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M39" s="16" t="s">
-        <v>60</v>
-      </c>
       <c r="N39" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2710,16 +2710,16 @@
         <v>190</v>
       </c>
       <c r="K40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L40" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M40" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2756,16 +2756,16 @@
         <v>20</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2802,16 +2802,16 @@
         <v>80</v>
       </c>
       <c r="K42" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L42" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N42" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2848,16 +2848,16 @@
         <v>250</v>
       </c>
       <c r="K43" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L43" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N43" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2894,39 +2894,63 @@
         <v>190</v>
       </c>
       <c r="K44" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L44" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="N44" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="14">
+        <v>410</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>220</v>
+      </c>
+      <c r="E45" s="14">
+        <v>220</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>250</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="508" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{412F799D-2833-4E01-91C8-6DF45D1106E4}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEDDBA60-C911-4603-83EC-8A394BB05B0D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>CA 2 annouced for DBMS.</t>
+  </si>
+  <si>
+    <t>Learned RAG in AI.</t>
   </si>
 </sst>
 </file>
@@ -2953,26 +2956,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>200</v>
+      </c>
+      <c r="E46" s="14">
+        <v>180</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12617058.xlsx
+++ b/12617058.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df999a3982f8b614/Desktop/Cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="520" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEDDBA60-C911-4603-83EC-8A394BB05B0D}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="8_{A6041FE9-1930-4897-81A2-42234A638A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E04F0C7-DA39-4EFE-B036-8EE205E0C52B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   <si>
     <t>Learned RAG in AI.</t>
   </si>
+  <si>
+    <t>Preparing for DBMS and communication skills CA.</t>
+  </si>
 </sst>
 </file>
 
@@ -617,6 +620,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3001,27 +3008,51 @@
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="14">
+        <v>350</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>320</v>
+      </c>
+      <c r="E47" s="14">
+        <v>120</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>300</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
